--- a/intake_forms/002_financial_services_intake_form--intake_forms.xlsx
+++ b/intake_forms/002_financial_services_intake_form--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'passive'}</t>
+          <t>passive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Passive'}</t>
+          <t>Passive</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'0-10k'}</t>
+          <t>0-10k</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '0-10k'}</t>
+          <t>0-10k</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'10-20k'}</t>
+          <t>10-20k</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '10-20k'}</t>
+          <t>10-20k</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'20-30k'}</t>
+          <t>20-30k</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '20-30k'}</t>
+          <t>20-30k</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'30-40k'}</t>
+          <t>30-40k</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '30-40k'}</t>
+          <t>30-40k</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'40-50k'}</t>
+          <t>40-50k</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '40-50k'}</t>
+          <t>40-50k</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'50-60k'}</t>
+          <t>50-60k</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '50-60k'}</t>
+          <t>50-60k</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'60-70k'}</t>
+          <t>60-70k</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '60-70k'}</t>
+          <t>60-70k</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'70-80k'}</t>
+          <t>70-80k</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '70-80k'}</t>
+          <t>70-80k</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'80-90k'}</t>
+          <t>80-90k</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '80-90k'}</t>
+          <t>80-90k</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'90-100k'}</t>
+          <t>90-100k</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '90-100k'}</t>
+          <t>90-100k</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'self-employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Self-Employed'}</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'disabled'}</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Disabled'}</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'salary'}</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Salary'}</t>
+          <t>Salary</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'investments'}</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Investments'}</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'rental_income'}</t>
+          <t>rental_income</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Rental Income'}</t>
+          <t>Rental Income</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'bank_of_america'}</t>
+          <t>bank_of_america</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Bank of America'}</t>
+          <t>Bank of America</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'wells_fargo'}</t>
+          <t>wells_fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Wells Fargo'}</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'chase'}</t>
+          <t>chase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Chase'}</t>
+          <t>Chase</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'credit_union'}</t>
+          <t>credit_union</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Union'}</t>
+          <t>Credit Union</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'stocks'}</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Stocks'}</t>
+          <t>Stocks</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'real_estate'}</t>
+          <t>real_estate</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Real Estate'}</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Primary'}</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Secondary'}</t>
+          <t>Secondary</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'investments'}</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Investments'}</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'real_estate'}</t>
+          <t>real_estate</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Real Estate'}</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
